--- a/WorkBot/refactor/data/orders/Sysco/Sysco_Downtown_2025-10-17.xlsx
+++ b/WorkBot/refactor/data/orders/Sysco/Sysco_Downtown_2025-10-17.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -659,6 +659,87 @@
         </is>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>7333506</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Oh Snap - Pickle Dill</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>5.56</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>5.56</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>7333486</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Oh Snap - Pickle Hottie</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>5.56</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>5.56</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>7333504</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Oh Snap - Pickle Sassy</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>5.56</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>5.56</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
